--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_17-08-2026.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_17-08-2026.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£21.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
